--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.21827875714585</v>
+        <v>6.210470298036201</v>
       </c>
       <c r="D2" t="n">
-        <v>26.26055463328012</v>
+        <v>4.267340127908019</v>
       </c>
       <c r="E2" t="n">
-        <v>14.41367511941671</v>
+        <v>2.342222206905216</v>
       </c>
       <c r="F2" t="n">
-        <v>8.656930298719853</v>
+        <v>1.406751173541976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.373339032019004</v>
+        <v>1.360667592703088</v>
       </c>
       <c r="D3" t="n">
-        <v>17.41595615713778</v>
+        <v>2.830092875534889</v>
       </c>
       <c r="E3" t="n">
-        <v>14.41367511941671</v>
+        <v>2.342222206905216</v>
       </c>
       <c r="F3" t="n">
-        <v>8.656930298719853</v>
+        <v>1.406751173541976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.6314391737934</v>
+        <v>6.440108865741428</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1478150704935</v>
+        <v>0.8365199489551939</v>
       </c>
       <c r="E4" t="n">
-        <v>14.41367511941671</v>
+        <v>2.342222206905216</v>
       </c>
       <c r="F4" t="n">
-        <v>8.656930298719853</v>
+        <v>1.406751173541976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
